--- a/X-ray spectrum calculations/Electron_energies.xlsx
+++ b/X-ray spectrum calculations/Electron_energies.xlsx
@@ -450,10 +450,10 @@
         <v>0.023</v>
       </c>
       <c r="B2" t="n">
-        <v>0.005538362036692515</v>
+        <v>0.01559859842046999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001857758399467987</v>
+        <v>0.0146219605534295</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>0.024</v>
       </c>
       <c r="B3" t="n">
-        <v>0.006488087125327864</v>
+        <v>0.01717892604717998</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001768920244805864</v>
+        <v>0.01480981132075472</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>0.025</v>
       </c>
       <c r="B4" t="n">
-        <v>0.007356332150971282</v>
+        <v>0.01822600357640807</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001664418666396238</v>
+        <v>0.01489200134998313</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         <v>0.026</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008214355237449348</v>
+        <v>0.01894180931083677</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001544056340318294</v>
+        <v>0.01484348142753096</v>
       </c>
     </row>
     <row r="6">
@@ -494,10 +494,10 @@
         <v>0.027</v>
       </c>
       <c r="B6" t="n">
-        <v>0.008986719137414532</v>
+        <v>0.01916677954251785</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001407633692354971</v>
+        <v>0.0146306049822064</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         <v>0.028</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0096891683561809</v>
+        <v>0.0189726462428486</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001254948873753232</v>
+        <v>0.01420709342560554</v>
       </c>
     </row>
     <row r="8">
@@ -516,10 +516,10 @@
         <v>0.029</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01029592699332301</v>
+        <v>0.01834679516568705</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001085797736732703</v>
+        <v>0.01350749403341289</v>
       </c>
     </row>
     <row r="9">
@@ -527,10 +527,10 @@
         <v>0.03</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0107935820320075</v>
+        <v>0.01731537072052034</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0008999738097401694</v>
+        <v>0.01243610223642173</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>0.031</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01123235788754067</v>
+        <v>0.01752306011480273</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0008794004996304607</v>
+        <v>0.01249592183517417</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +549,10 @@
         <v>0.032</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01159893039228287</v>
+        <v>0.01758143020234878</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0008554529950093838</v>
+        <v>0.01251066809736262</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +560,10 @@
         <v>0.033</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01189355645956531</v>
+        <v>0.01750034186686389</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0008281206006539104</v>
+        <v>0.01247611601292915</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +571,10 @@
         <v>0.034</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01212760450429383</v>
+        <v>0.01730550680569929</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0007973925909591402</v>
+        <v>0.01238749549116268</v>
       </c>
     </row>
     <row r="14">
@@ -582,10 +582,10 @@
         <v>0.035</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01229142957182608</v>
+        <v>0.01699160269116004</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0007632582098571337</v>
+        <v>0.01223940052803231</v>
       </c>
     </row>
     <row r="15">
@@ -593,10 +593,10 @@
         <v>0.036</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01238428233161273</v>
+        <v>0.01656696449431792</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0007257066707355152</v>
+        <v>0.01202567958357432</v>
       </c>
     </row>
     <row r="16">
@@ -604,10 +604,10 @@
         <v>0.037</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01246060700042513</v>
+        <v>0.01611146635465378</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0006847271563558766</v>
+        <v>0.01173930247262804</v>
       </c>
     </row>
     <row r="17">
@@ -615,10 +615,10 @@
         <v>0.038</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0124857202785505</v>
+        <v>0.0155840127256416</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0006403088187719727</v>
+        <v>0.01137219768083932</v>
       </c>
     </row>
     <row r="18">
@@ -626,10 +626,10 @@
         <v>0.039</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01246434294844975</v>
+        <v>0.01499716362036412</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0005924407792477044</v>
+        <v>0.01091505214493065</v>
       </c>
     </row>
     <row r="19">
@@ -637,10 +637,10 @@
         <v>0.04</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01241554012024277</v>
+        <v>0.01437927131868553</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0005411121281748881</v>
+        <v>0.01035706298919121</v>
       </c>
     </row>
     <row r="20">
@@ -648,10 +648,10 @@
         <v>0.041</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01235459813713632</v>
+        <v>0.01409368205566036</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0005331105549355267</v>
+        <v>0.01035957752877044</v>
       </c>
     </row>
     <row r="21">
@@ -659,10 +659,10 @@
         <v>0.042</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01225574002823274</v>
+        <v>0.01376744377831037</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0005240405996678117</v>
+        <v>0.01034121990616107</v>
       </c>
     </row>
     <row r="22">
@@ -670,10 +670,10 @@
         <v>0.043</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01213895150975542</v>
+        <v>0.01342464432734222</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0005139009492527666</v>
+        <v>0.01030097702047835</v>
       </c>
     </row>
     <row r="23">
@@ -681,10 +681,10 @@
         <v>0.044</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01200939225777274</v>
+        <v>0.0130718424433866</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0005026902891290262</v>
+        <v>0.01023776912687694</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +692,10 @@
         <v>0.045</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01186354041870276</v>
+        <v>0.0127059400746379</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0004904073032913523</v>
+        <v>0.01015044426494346</v>
       </c>
     </row>
     <row r="25">
@@ -703,10 +703,10 @@
         <v>0.046</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01171437011577136</v>
+        <v>0.01234146550660577</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0004770506742891366</v>
+        <v>0.01003777211862318</v>
       </c>
     </row>
     <row r="26">
@@ -714,10 +714,10 @@
         <v>0.047</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01154366191190722</v>
+        <v>0.01195972293785576</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0004626190832249171</v>
+        <v>0.009898437238843391</v>
       </c>
     </row>
     <row r="27">
@@ -725,10 +725,10 @@
         <v>0.048</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01136647735115226</v>
+        <v>0.011577190481099</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0004471112097528777</v>
+        <v>0.009731031550301895</v>
       </c>
     </row>
     <row r="28">
@@ -736,10 +736,10 @@
         <v>0.049</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01119403498230247</v>
+        <v>0.01120544577906411</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0004305257320773594</v>
+        <v>0.009534046052631577</v>
       </c>
     </row>
     <row r="29">
@@ -747,10 +747,10 @@
         <v>0.05</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01101416353629198</v>
+        <v>0.01083227669450344</v>
       </c>
       <c r="C29" t="n">
-        <v>0.000412861326951362</v>
+        <v>0.009305861613045394</v>
       </c>
     </row>
     <row r="30">
@@ -758,10 +758,10 @@
         <v>0.051</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01082273099037723</v>
+        <v>0.01054769138833927</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0004109030843170131</v>
+        <v>0.009346294483985764</v>
       </c>
     </row>
     <row r="31">
@@ -769,10 +769,10 @@
         <v>0.052</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01063322850586316</v>
+        <v>0.01026833737419973</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0004085398802535934</v>
+        <v>0.009378212842388864</v>
       </c>
     </row>
     <row r="32">
@@ -780,10 +780,10 @@
         <v>0.053</v>
       </c>
       <c r="B32" t="n">
-        <v>0.01044786660787036</v>
+        <v>0.009996280191109163</v>
       </c>
       <c r="C32" t="n">
-        <v>0.000405771461662784</v>
+        <v>0.009401373526745241</v>
       </c>
     </row>
     <row r="33">
@@ -791,10 +791,10 @@
         <v>0.054</v>
       </c>
       <c r="B33" t="n">
-        <v>0.01025762228611244</v>
+        <v>0.00972285865458202</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0004025975753050808</v>
+        <v>0.009415524027459954</v>
       </c>
     </row>
     <row r="34">
@@ -802,10 +802,10 @@
         <v>0.055</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0100717925917624</v>
+        <v>0.009456934887649114</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0003990179677997207</v>
+        <v>0.009420402033271718</v>
       </c>
     </row>
     <row r="35">
@@ -813,10 +813,10 @@
         <v>0.056</v>
       </c>
       <c r="B35" t="n">
-        <v>0.009876954873736956</v>
+        <v>0.009185909373521949</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0003950323856246094</v>
+        <v>0.009415734951003266</v>
       </c>
     </row>
     <row r="36">
@@ -824,10 +824,10 @@
         <v>0.057</v>
       </c>
       <c r="B36" t="n">
-        <v>0.009689483075011628</v>
+        <v>0.008925107534604616</v>
       </c>
       <c r="C36" t="n">
-        <v>0.000390640575116246</v>
+        <v>0.009401239396795475</v>
       </c>
     </row>
     <row r="37">
@@ -835,10 +835,10 @@
         <v>0.058</v>
       </c>
       <c r="B37" t="n">
-        <v>0.05908630881987439</v>
+        <v>0.05389778799536693</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0003858422824696498</v>
+        <v>0.009376620656830079</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         <v>0.059</v>
       </c>
       <c r="B38" t="n">
-        <v>0.09569851382335628</v>
+        <v>0.08644047087555518</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0003806372537382856</v>
+        <v>0.009341572115384614</v>
       </c>
     </row>
     <row r="39">
@@ -857,10 +857,10 @@
         <v>0.06</v>
       </c>
       <c r="B39" t="n">
-        <v>0.009143958659890213</v>
+        <v>0.008177673536690843</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0003750252348339887</v>
+        <v>0.009295774647887323</v>
       </c>
     </row>
     <row r="40">
@@ -868,10 +868,10 @@
         <v>0.061</v>
       </c>
       <c r="B40" t="n">
-        <v>0.008961224771181206</v>
+        <v>0.007971924222821582</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0003777734672398228</v>
+        <v>0.009413611504467992</v>
       </c>
     </row>
     <row r="41">
@@ -879,10 +879,10 @@
         <v>0.062</v>
       </c>
       <c r="B41" t="n">
-        <v>0.008788797388942405</v>
+        <v>0.007777011884418436</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0003804060857901159</v>
+        <v>0.009529821288295364</v>
       </c>
     </row>
     <row r="42">
@@ -890,10 +890,10 @@
         <v>0.063</v>
       </c>
       <c r="B42" t="n">
-        <v>0.008611664210853687</v>
+        <v>0.007579577874450889</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0003829230521776503</v>
+        <v>0.009644377252307842</v>
       </c>
     </row>
     <row r="43">
@@ -901,10 +901,10 @@
         <v>0.064</v>
       </c>
       <c r="B43" t="n">
-        <v>0.008448522104593551</v>
+        <v>0.007396057184284978</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0003853243280838939</v>
+        <v>0.009757252059962274</v>
       </c>
     </row>
     <row r="44">
@@ -912,10 +912,10 @@
         <v>0.065</v>
       </c>
       <c r="B44" t="n">
-        <v>0.008274933260003258</v>
+        <v>0.007204973974393985</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0003876098751790031</v>
+        <v>0.009868417768904417</v>
       </c>
     </row>
     <row r="45">
@@ -923,10 +923,10 @@
         <v>0.066</v>
       </c>
       <c r="B45" t="n">
-        <v>0.008115580625378409</v>
+        <v>0.007027851647099815</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0003897796551218172</v>
+        <v>0.009977845814093554</v>
       </c>
     </row>
     <row r="46">
@@ -934,10 +934,10 @@
         <v>0.067</v>
       </c>
       <c r="B46" t="n">
-        <v>0.03635732556948143</v>
+        <v>0.03131241120924264</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0003918336295598526</v>
+        <v>0.01008550699035986</v>
       </c>
     </row>
     <row r="47">
@@ -945,10 +945,10 @@
         <v>0.068</v>
       </c>
       <c r="B47" t="n">
-        <v>0.007797248950931172</v>
+        <v>0.006678423376411581</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0003937717601293032</v>
+        <v>0.01019137143437215</v>
       </c>
     </row>
     <row r="48">
@@ -956,10 +956,10 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="B48" t="n">
-        <v>0.01504128000294353</v>
+        <v>0.01281184051483817</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0003955940084550368</v>
+        <v>0.01029540860599255</v>
       </c>
     </row>
     <row r="49">
@@ -967,10 +967,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B49" t="n">
-        <v>0.006230308852573631</v>
+        <v>0.00527735785919525</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0003973003361505894</v>
+        <v>0.01039758726899384</v>
       </c>
     </row>
     <row r="50">
@@ -978,10 +978,10 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="B50" t="n">
-        <v>0.00614472888100454</v>
+        <v>0.005175780324555855</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0003988907048181647</v>
+        <v>0.01049787547111363</v>
       </c>
     </row>
     <row r="51">
@@ -989,10 +989,10 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="B51" t="n">
-        <v>0.006055125004385435</v>
+        <v>0.00507163631110997</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0004003650760486304</v>
+        <v>0.01059624052341884</v>
       </c>
     </row>
     <row r="52">
@@ -1000,10 +1000,10 @@
         <v>0.073</v>
       </c>
       <c r="B52" t="n">
-        <v>0.005976760015534374</v>
+        <v>0.00497769474641948</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0004017234114215146</v>
+        <v>0.01069264897895232</v>
       </c>
     </row>
     <row r="53">
@@ -1011,10 +1011,10 @@
         <v>0.074</v>
       </c>
       <c r="B53" t="n">
-        <v>0.005891044093994185</v>
+        <v>0.004878401880927759</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0004029656725050018</v>
+        <v>0.01078706661063249</v>
       </c>
     </row>
     <row r="54">
@@ -1022,10 +1022,10 @@
         <v>0.075</v>
       </c>
       <c r="B54" t="n">
-        <v>0.005809075895672962</v>
+        <v>0.004783000710484879</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0004040918208559332</v>
+        <v>0.01087945838837517</v>
       </c>
     </row>
     <row r="55">
@@ -1033,10 +1033,10 @@
         <v>0.076</v>
       </c>
       <c r="B55" t="n">
-        <v>0.005722162115726026</v>
+        <v>0.004684321641162158</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0004051018180197999</v>
+        <v>0.01096978845540555</v>
       </c>
     </row>
     <row r="56">
@@ -1044,10 +1044,10 @@
         <v>0.077</v>
       </c>
       <c r="B56" t="n">
-        <v>0.005641046013286636</v>
+        <v>0.004591179065343</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0004059956255307389</v>
+        <v>0.01105802010372668</v>
       </c>
     </row>
     <row r="57">
@@ -1055,10 +1055,10 @@
         <v>0.078</v>
       </c>
       <c r="B57" t="n">
-        <v>0.005558728841023858</v>
+        <v>0.004497827780285089</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0004067732049115342</v>
+        <v>0.01114411574870912</v>
       </c>
     </row>
     <row r="58">
@@ -1066,10 +1066,10 @@
         <v>0.079</v>
       </c>
       <c r="B58" t="n">
-        <v>0.005474552258526478</v>
+        <v>0.004403755555557989</v>
       </c>
       <c r="C58" t="n">
-        <v>0.000407434517673612</v>
+        <v>0.011228036902765</v>
       </c>
     </row>
     <row r="59">
@@ -1077,10 +1077,10 @@
         <v>0.08</v>
       </c>
       <c r="B59" t="n">
-        <v>0.005390917334969056</v>
+        <v>0.004310909151016624</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0004079795253170356</v>
+        <v>0.0113097441480675</v>
       </c>
     </row>
     <row r="60">
@@ -1088,10 +1088,10 @@
         <v>0.081</v>
       </c>
       <c r="B60" t="n">
-        <v>0.005308311135208672</v>
+        <v>0.004230105528564645</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0004127003266349695</v>
+        <v>0.01148049440043704</v>
       </c>
     </row>
     <row r="61">
@@ -1099,10 +1099,10 @@
         <v>0.082</v>
       </c>
       <c r="B61" t="n">
-        <v>0.005230952390238167</v>
+        <v>0.004153926013657884</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0004174117206167498</v>
+        <v>0.01165218201754386</v>
       </c>
     </row>
     <row r="62">
@@ -1110,10 +1110,10 @@
         <v>0.083</v>
       </c>
       <c r="B62" t="n">
-        <v>0.005148875003751181</v>
+        <v>0.004074440516781241</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0004221137053998468</v>
+        <v>0.01182481705639615</v>
       </c>
     </row>
     <row r="63">
@@ -1121,10 +1121,10 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="B63" t="n">
-        <v>0.005068281291751909</v>
+        <v>0.003996579281620448</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0004268062791214102</v>
+        <v>0.01199840971838763</v>
       </c>
     </row>
     <row r="64">
@@ -1132,10 +1132,10 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="B64" t="n">
-        <v>0.004988393020941239</v>
+        <v>0.003919718514755092</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0004314894399182612</v>
+        <v>0.01217297035189803</v>
       </c>
     </row>
     <row r="65">
@@ -1143,10 +1143,10 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="B65" t="n">
-        <v>0.004910467996169868</v>
+        <v>0.003844837266329362</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0004361631859268999</v>
+        <v>0.01234850945494995</v>
       </c>
     </row>
     <row r="66">
@@ -1154,10 +1154,10 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="B66" t="n">
-        <v>0.004834796315407615</v>
+        <v>0.003772145584797161</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0004408275152834951</v>
+        <v>0.01252503767792353</v>
       </c>
     </row>
     <row r="67">
@@ -1165,10 +1165,10 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="B67" t="n">
-        <v>0.004758122672653658</v>
+        <v>0.003699093994349326</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0004454824261238967</v>
+        <v>0.01270256582633053</v>
       </c>
     </row>
     <row r="68">
@@ -1176,10 +1176,10 @@
         <v>0.089</v>
       </c>
       <c r="B68" t="n">
-        <v>0.004680304695103623</v>
+        <v>0.003625580647372509</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0004501279165836231</v>
+        <v>0.01288110486364914</v>
       </c>
     </row>
     <row r="69">
@@ -1187,10 +1187,10 @@
         <v>0.09</v>
       </c>
       <c r="B69" t="n">
-        <v>0.004608482432420603</v>
+        <v>0.003557126329430161</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0004547639847978717</v>
+        <v>0.01306066591422122</v>
       </c>
     </row>
     <row r="70">
@@ -1198,10 +1198,10 @@
         <v>0.091</v>
       </c>
       <c r="B70" t="n">
-        <v>0.004533688538873303</v>
+        <v>0.003486784454502811</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0004593906289015115</v>
+        <v>0.01324126026621354</v>
       </c>
     </row>
     <row r="71">
@@ -1209,10 +1209,10 @@
         <v>0.092</v>
       </c>
       <c r="B71" t="n">
-        <v>0.004461393127471979</v>
+        <v>0.0034187716566123</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0004640078470290851</v>
+        <v>0.01342289937464468</v>
       </c>
     </row>
     <row r="72">
@@ -1220,10 +1220,10 @@
         <v>0.093</v>
       </c>
       <c r="B72" t="n">
-        <v>0.004389958375730195</v>
+        <v>0.003351816653052064</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0004686156373148131</v>
+        <v>0.01360559486447931</v>
       </c>
     </row>
     <row r="73">
@@ -1231,10 +1231,10 @@
         <v>0.094</v>
       </c>
       <c r="B73" t="n">
-        <v>0.004318133972102749</v>
+        <v>0.003284961179772555</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0004732139978925867</v>
+        <v>0.01378935853379152</v>
       </c>
     </row>
     <row r="74">
@@ -1242,10 +1242,10 @@
         <v>0.095</v>
       </c>
       <c r="B74" t="n">
-        <v>0.004252129725899329</v>
+        <v>0.003222915312206552</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0004778029268959746</v>
+        <v>0.01397420235699914</v>
       </c>
     </row>
     <row r="75">
@@ -1253,10 +1253,10 @@
         <v>0.096</v>
       </c>
       <c r="B75" t="n">
-        <v>0.004182019148285468</v>
+        <v>0.003158134343731849</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0004823824224582148</v>
+        <v>0.01416013848817081</v>
       </c>
     </row>
     <row r="76">
@@ -1264,10 +1264,10 @@
         <v>0.097</v>
       </c>
       <c r="B76" t="n">
-        <v>0.004113428641214576</v>
+        <v>0.003094885865245691</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0004869524827122222</v>
+        <v>0.01434717926440776</v>
       </c>
     </row>
     <row r="77">
@@ -1275,10 +1275,10 @@
         <v>0.098</v>
       </c>
       <c r="B77" t="n">
-        <v>0.004047465072955263</v>
+        <v>0.003033986966668145</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0004915131057905891</v>
+        <v>0.01453533720930233</v>
       </c>
     </row>
     <row r="78">
@@ -1286,10 +1286,10 @@
         <v>0.099</v>
       </c>
       <c r="B78" t="n">
-        <v>0.003981411585030028</v>
+        <v>0.00297338678115745</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0004960642898255742</v>
+        <v>0.01472462503647505</v>
       </c>
     </row>
     <row r="79">
@@ -1297,10 +1297,10 @@
         <v>0.1</v>
       </c>
       <c r="B79" t="n">
-        <v>0.003918362912607688</v>
+        <v>0.002915388714449239</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0005006060329491168</v>
+        <v>0.01491505565319274</v>
       </c>
     </row>
     <row r="80">
@@ -1308,10 +1308,10 @@
         <v>0.101</v>
       </c>
       <c r="B80" t="n">
-        <v>0.003855185783519745</v>
+        <v>0.002861709166950108</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0005064982948542709</v>
+        <v>0.01512580213275708</v>
       </c>
     </row>
     <row r="81">
@@ -1319,10 +1319,10 @@
         <v>0.102</v>
       </c>
       <c r="B81" t="n">
-        <v>0.003792380108289837</v>
+        <v>0.002808522908742211</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0005124081766647601</v>
+        <v>0.01533806418195089</v>
       </c>
     </row>
     <row r="82">
@@ -1330,10 +1330,10 @@
         <v>0.103</v>
       </c>
       <c r="B82" t="n">
-        <v>0.003730073273111354</v>
+        <v>0.002755922154747458</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0005183356804851749</v>
+        <v>0.01555185263853488</v>
       </c>
     </row>
     <row r="83">
@@ -1341,10 +1341,10 @@
         <v>0.104</v>
       </c>
       <c r="B83" t="n">
-        <v>0.003671100958877481</v>
+        <v>0.002705994540512657</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0005242808084203227</v>
+        <v>0.0157671784438504</v>
       </c>
     </row>
     <row r="84">
@@ -1352,10 +1352,10 @@
         <v>0.105</v>
       </c>
       <c r="B84" t="n">
-        <v>0.003610815175237817</v>
+        <v>0.002655304751471415</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0005302435625752401</v>
+        <v>0.01598405264405976</v>
       </c>
     </row>
     <row r="85">
@@ -1363,10 +1363,10 @@
         <v>0.106</v>
       </c>
       <c r="B85" t="n">
-        <v>0.003551442504396147</v>
+        <v>0.002605493154182216</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0005362239450551899</v>
+        <v>0.0162024863914046</v>
       </c>
     </row>
     <row r="86">
@@ -1374,10 +1374,10 @@
         <v>0.107</v>
       </c>
       <c r="B86" t="n">
-        <v>0.003493248423461384</v>
+        <v>0.00255674933533548</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0005422219579656603</v>
+        <v>0.01642249094548227</v>
       </c>
     </row>
     <row r="87">
@@ -1385,10 +1385,10 @@
         <v>0.108</v>
       </c>
       <c r="B87" t="n">
-        <v>0.003436046670268404</v>
+        <v>0.002508931190742165</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0005482376034123584</v>
+        <v>0.01664407767454081</v>
       </c>
     </row>
     <row r="88">
@@ -1396,10 +1396,10 @@
         <v>0.109</v>
       </c>
       <c r="B88" t="n">
-        <v>0.003380275067952469</v>
+        <v>0.002462352519117936</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0005542708835012259</v>
+        <v>0.01686725805679261</v>
       </c>
     </row>
     <row r="89">
@@ -1407,10 +1407,10 @@
         <v>0.11</v>
       </c>
       <c r="B89" t="n">
-        <v>0.003324684375440592</v>
+        <v>0.002416098069577501</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0005603218003384217</v>
+        <v>0.01709204368174727</v>
       </c>
     </row>
     <row r="90">
@@ -1418,10 +1418,10 @@
         <v>0.111</v>
       </c>
       <c r="B90" t="n">
-        <v>0.003271372718270954</v>
+        <v>0.002371688029558376</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0005663903560303341</v>
+        <v>0.01731844625156385</v>
       </c>
     </row>
     <row r="91">
@@ -1429,10 +1429,10 @@
         <v>0.112</v>
       </c>
       <c r="B91" t="n">
-        <v>0.003218073906767875</v>
+        <v>0.002327471554713235</v>
       </c>
       <c r="C91" t="n">
-        <v>0.000572476552683577</v>
+        <v>0.01754647758242289</v>
       </c>
     </row>
     <row r="92">
@@ -1440,10 +1440,10 @@
         <v>0.113</v>
       </c>
       <c r="B92" t="n">
-        <v>0.003165704265145992</v>
+        <v>0.00228410974420483</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0005785803924049852</v>
+        <v>0.01777614960591848</v>
       </c>
     </row>
     <row r="93">
@@ -1451,10 +1451,10 @@
         <v>0.114</v>
       </c>
       <c r="B93" t="n">
-        <v>0.003112829360639403</v>
+        <v>0.002240565307846131</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0005847018773016269</v>
+        <v>0.01800747437047091</v>
       </c>
     </row>
     <row r="94">
@@ -1462,10 +1462,10 @@
         <v>0.115</v>
       </c>
       <c r="B94" t="n">
-        <v>0.003061860967144804</v>
+        <v>0.002198572671482781</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0005908410094807849</v>
+        <v>0.01824046404275997</v>
       </c>
     </row>
     <row r="95">
@@ -1473,10 +1473,10 @@
         <v>0.116</v>
       </c>
       <c r="B95" t="n">
-        <v>0.003011833518725747</v>
+        <v>0.002157430292015047</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0005969977910499772</v>
+        <v>0.01847513090917947</v>
       </c>
     </row>
     <row r="96">
@@ -1484,10 +1484,10 @@
         <v>0.117</v>
       </c>
       <c r="B96" t="n">
-        <v>0.002962907586214235</v>
+        <v>0.002117248039322826</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0006031722241169429</v>
+        <v>0.01871148737731335</v>
       </c>
     </row>
     <row r="97">
@@ -1495,10 +1495,10 @@
         <v>0.118</v>
       </c>
       <c r="B97" t="n">
-        <v>0.00291386925412032</v>
+        <v>0.002077154865042612</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0006093643107896449</v>
+        <v>0.01894954597743349</v>
       </c>
     </row>
     <row r="98">
@@ -1506,10 +1506,10 @@
         <v>0.119</v>
       </c>
       <c r="B98" t="n">
-        <v>0.002865704427352505</v>
+        <v>0.002037852468474196</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0006155740531762737</v>
+        <v>0.01918931936402002</v>
       </c>
     </row>
     <row r="99">
@@ -1517,10 +1517,10 @@
         <v>0.12</v>
       </c>
       <c r="B99" t="n">
-        <v>0.002818766361741198</v>
+        <v>0.001999586920770958</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0006218014533852453</v>
+        <v>0.01943082031730415</v>
       </c>
     </row>
     <row r="100">
@@ -1528,10 +1528,10 @@
         <v>0.121</v>
       </c>
       <c r="B100" t="n">
-        <v>0.002772190115738006</v>
+        <v>0.00196173978517712</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0006280465135252002</v>
+        <v>0.01967406174483404</v>
       </c>
     </row>
     <row r="101">
@@ -1539,10 +1539,10 @@
         <v>0.122</v>
       </c>
       <c r="B101" t="n">
-        <v>0.002727174618221889</v>
+        <v>0.001925155541948005</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0006343092357050066</v>
+        <v>0.0199190566830643</v>
       </c>
     </row>
     <row r="102">
@@ -1550,10 +1550,10 @@
         <v>0.123</v>
       </c>
       <c r="B102" t="n">
-        <v>0.0026818968550135</v>
+        <v>0.001888542357763172</v>
       </c>
       <c r="C102" t="n">
-        <v>0.000640589622033754</v>
+        <v>0.02016581829896907</v>
       </c>
     </row>
     <row r="103">
@@ -1561,10 +1561,10 @@
         <v>0.124</v>
       </c>
       <c r="B103" t="n">
-        <v>0.002636523819778122</v>
+        <v>0.00185201892031646</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0006468876746207629</v>
+        <v>0.02041435989167971</v>
       </c>
     </row>
     <row r="104">
@@ -1572,10 +1572,10 @@
         <v>0.125</v>
       </c>
       <c r="B104" t="n">
-        <v>0.002593959703630594</v>
+        <v>0.001817620748216518</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0006532033955755736</v>
+        <v>0.02066469489414695</v>
       </c>
     </row>
     <row r="105">
@@ -1583,10 +1583,10 @@
         <v>0.126</v>
       </c>
       <c r="B105" t="n">
-        <v>0.002550119584604744</v>
+        <v>0.001782477972072477</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0006595367870079544</v>
+        <v>0.02091683687482834</v>
       </c>
     </row>
     <row r="106">
@@ -1594,10 +1594,10 @@
         <v>0.127</v>
       </c>
       <c r="B106" t="n">
-        <v>0.00250813994628571</v>
+        <v>0.001748784142990044</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0006658878510279008</v>
+        <v>0.02117079953940122</v>
       </c>
     </row>
     <row r="107">
@@ -1605,10 +1605,10 @@
         <v>0.128</v>
       </c>
       <c r="B107" t="n">
-        <v>0.00246751980767764</v>
+        <v>0.00171618115965375</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0006722565897456344</v>
+        <v>0.02142659673250182</v>
       </c>
     </row>
     <row r="108">
@@ -1616,10 +1616,10 @@
         <v>0.129</v>
       </c>
       <c r="B108" t="n">
-        <v>0.002425193336361478</v>
+        <v>0.001682534969984056</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0006786430052715991</v>
+        <v>0.02168424243949077</v>
       </c>
     </row>
     <row r="109">
@@ -1627,10 +1627,10 @@
         <v>0.13</v>
       </c>
       <c r="B109" t="n">
-        <v>0.002385365347191292</v>
+        <v>0.001650764366587047</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0006850470997164643</v>
+        <v>0.02194375078824568</v>
       </c>
     </row>
     <row r="110">
@@ -1638,10 +1638,10 @@
         <v>0.131</v>
       </c>
       <c r="B110" t="n">
-        <v>0.00234464886608402</v>
+        <v>0.00161851832173999</v>
       </c>
       <c r="C110" t="n">
-        <v>0.0006914688751911297</v>
+        <v>0.02220513605098119</v>
       </c>
     </row>
     <row r="111">
@@ -1649,10 +1649,10 @@
         <v>0.132</v>
       </c>
       <c r="B111" t="n">
-        <v>0.002306724176509184</v>
+        <v>0.00158833560202309</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0006979083338067185</v>
+        <v>0.02246841264609691</v>
       </c>
     </row>
     <row r="112">
@@ -1660,10 +1660,10 @@
         <v>0.133</v>
       </c>
       <c r="B112" t="n">
-        <v>0.002266901539700066</v>
+        <v>0.001556980625494543</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0007043654776745751</v>
+        <v>0.02273359514005389</v>
       </c>
     </row>
     <row r="113">
@@ -1671,10 +1671,10 @@
         <v>0.134</v>
       </c>
       <c r="B113" t="n">
-        <v>0.002229102095374194</v>
+        <v>0.001527149649425065</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0007108403089062769</v>
+        <v>0.02300069824928009</v>
       </c>
     </row>
     <row r="114">
@@ -1682,10 +1682,10 @@
         <v>0.135</v>
       </c>
       <c r="B114" t="n">
-        <v>0.002191016834967354</v>
+        <v>0.001497254269429071</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0007173328296136216</v>
+        <v>0.02326973684210526</v>
       </c>
     </row>
     <row r="115">
@@ -1693,10 +1693,10 @@
         <v>0.136</v>
       </c>
       <c r="B115" t="n">
-        <v>0.002154841296989145</v>
+        <v>0.001468792522658652</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0007238430419086351</v>
+        <v>0.02354072594072595</v>
       </c>
     </row>
     <row r="116">
@@ -1704,10 +1704,10 @@
         <v>0.137</v>
       </c>
       <c r="B116" t="n">
-        <v>0.00211750964902051</v>
+        <v>0.001439670054831513</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0007303709479035708</v>
+        <v>0.02381368072320099</v>
       </c>
     </row>
     <row r="117">
@@ -1715,10 +1715,10 @@
         <v>0.138</v>
       </c>
       <c r="B117" t="n">
-        <v>0.002082187277396347</v>
+        <v>0.001412039516307128</v>
       </c>
       <c r="C117" t="n">
-        <v>0.0007369165497109055</v>
+        <v>0.02408861652547828</v>
       </c>
     </row>
     <row r="118">
@@ -1726,10 +1726,10 @@
         <v>0.139</v>
       </c>
       <c r="B118" t="n">
-        <v>0.002045928242585496</v>
+        <v>0.001383897776446745</v>
       </c>
       <c r="C118" t="n">
-        <v>0.0007434798494433417</v>
+        <v>0.02436554884345312</v>
       </c>
     </row>
     <row r="119">
@@ -1737,10 +1737,10 @@
         <v>0.14</v>
       </c>
       <c r="B119" t="n">
-        <v>0.002012574469361698</v>
+        <v>0.001357841795915804</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0007500608492138098</v>
+        <v>0.02464449333505889</v>
       </c>
     </row>
     <row r="120">
@@ -1748,10 +1748,10 @@
         <v>0.141</v>
       </c>
       <c r="B120" t="n">
-        <v>0.001977112936349799</v>
+        <v>0.001330482978930847</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0007566595511354629</v>
+        <v>0.02492546582239062</v>
       </c>
     </row>
     <row r="121">
@@ -1759,10 +1759,10 @@
         <v>0.142</v>
       </c>
       <c r="B121" t="n">
-        <v>0.001943284943935483</v>
+        <v>0.001304343503396825</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0007632759573216829</v>
+        <v>0.02520848229386205</v>
       </c>
     </row>
     <row r="122">
@@ -1770,10 +1770,10 @@
         <v>0.143</v>
       </c>
       <c r="B122" t="n">
-        <v>0.001909443035382393</v>
+        <v>0.001278311951527034</v>
       </c>
       <c r="C122" t="n">
-        <v>0.000769910069886077</v>
+        <v>0.02549355890639675</v>
       </c>
     </row>
     <row r="123">
@@ -1781,10 +1781,10 @@
         <v>0.144</v>
       </c>
       <c r="B123" t="n">
-        <v>0.001877735648422739</v>
+        <v>0.001253822989326548</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0007765618909424777</v>
+        <v>0.025780711987654</v>
       </c>
     </row>
     <row r="124">
@@ -1792,10 +1792,10 @@
         <v>0.145</v>
       </c>
       <c r="B124" t="n">
-        <v>0.00184450283855905</v>
+        <v>0.001228428004883137</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0007832314226049416</v>
+        <v>0.02606995803829006</v>
       </c>
     </row>
     <row r="125">
@@ -1803,10 +1803,10 @@
         <v>0.146</v>
       </c>
       <c r="B125" t="n">
-        <v>0.00181162328452577</v>
+        <v>0.001203382887292152</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0007899186669877575</v>
+        <v>0.02636131373425544</v>
       </c>
     </row>
     <row r="126">
@@ -1814,10 +1814,10 @@
         <v>0.147</v>
       </c>
       <c r="B126" t="n">
-        <v>0.001780458626978288</v>
+        <v>0.001179587922130453</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0007966236262054366</v>
+        <v>0.02665479592912888</v>
       </c>
     </row>
     <row r="127">
@@ -1825,10 +1825,10 @@
         <v>0.148</v>
       </c>
       <c r="B127" t="n">
-        <v>0.001749149455682003</v>
+        <v>0.001155805519559839</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0008033463023727132</v>
+        <v>0.02695042165648876</v>
       </c>
     </row>
     <row r="128">
@@ -1836,10 +1836,10 @@
         <v>0.149</v>
       </c>
       <c r="B128" t="n">
-        <v>0.001719004958153851</v>
+        <v>0.001132899257793972</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0008100866976045493</v>
+        <v>0.02724820813232254</v>
       </c>
     </row>
     <row r="129">
@@ -1847,10 +1847,10 @@
         <v>0.15</v>
       </c>
       <c r="B129" t="n">
-        <v>0.001687916304133517</v>
+        <v>0.001109476931444556</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0008168448140161404</v>
+        <v>0.02754817275747508</v>
       </c>
     </row>
     <row r="130">
@@ -1858,10 +1858,10 @@
         <v>0.151</v>
       </c>
       <c r="B130" t="n">
-        <v>0.001658121851019133</v>
+        <v>0.001087966806880603</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0008235204200749349</v>
+        <v>0.02782247620315516</v>
       </c>
     </row>
     <row r="131">
@@ -1869,10 +1869,10 @@
         <v>0.152</v>
       </c>
       <c r="B131" t="n">
-        <v>0.001628198941239147</v>
+        <v>0.001066441661351207</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0008302123833082034</v>
+        <v>0.02809830888236864</v>
       </c>
     </row>
     <row r="132">
@@ -1880,10 +1880,10 @@
         <v>0.153</v>
       </c>
       <c r="B132" t="n">
-        <v>0.001599432141449586</v>
+        <v>0.001045741824404894</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0008369207050246904</v>
+        <v>0.02837567907007816</v>
       </c>
     </row>
     <row r="133">
@@ -1891,10 +1891,10 @@
         <v>0.154</v>
       </c>
       <c r="B133" t="n">
-        <v>0.001570921184519018</v>
+        <v>0.001025275704865617</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0008436453865332351</v>
+        <v>0.02865459510105742</v>
       </c>
     </row>
     <row r="134">
@@ -1902,10 +1902,10 @@
         <v>0.155</v>
       </c>
       <c r="B134" t="n">
-        <v>0.001541754028121661</v>
+        <v>0.001004448223496111</v>
       </c>
       <c r="C134" t="n">
-        <v>0.000850386429142764</v>
+        <v>0.02893506537043245</v>
       </c>
     </row>
     <row r="135">
@@ -1913,10 +1913,10 @@
         <v>0.156</v>
       </c>
       <c r="B135" t="n">
-        <v>0.001513410064856377</v>
+        <v>0.0009842237740040796</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0008571438341623076</v>
+        <v>0.02921709833422892</v>
       </c>
     </row>
     <row r="136">
@@ -1924,10 +1924,10 @@
         <v>0.157</v>
       </c>
       <c r="B136" t="n">
-        <v>0.001486683585105476</v>
+        <v>0.0009651151243203947</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0008639176029009827</v>
+        <v>0.02950070250992531</v>
       </c>
     </row>
     <row r="137">
@@ -1935,10 +1935,10 @@
         <v>0.158</v>
       </c>
       <c r="B137" t="n">
-        <v>0.001459101798056103</v>
+        <v>0.0009455142450369594</v>
       </c>
       <c r="C137" t="n">
-        <v>0.0008707077366679979</v>
+        <v>0.02978588647701227</v>
       </c>
     </row>
     <row r="138">
@@ -1946,10 +1946,10 @@
         <v>0.159</v>
       </c>
       <c r="B138" t="n">
-        <v>0.00143215158961261</v>
+        <v>0.0009263859137777385</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0008775142367726649</v>
+        <v>0.03007265887755791</v>
       </c>
     </row>
     <row r="139">
@@ -1957,10 +1957,10 @@
         <v>0.16</v>
       </c>
       <c r="B139" t="n">
-        <v>0.001404933763115778</v>
+        <v>0.0009071473342408528</v>
       </c>
       <c r="C139" t="n">
-        <v>0.0008843371045243799</v>
+        <v>0.03036102841677943</v>
       </c>
     </row>
     <row r="140">
@@ -1968,10 +1968,10 @@
         <v>0.161</v>
       </c>
       <c r="B140" t="n">
-        <v>0.001378222269975864</v>
+        <v>0.0008882982753780135</v>
       </c>
       <c r="C140" t="n">
-        <v>0.000891176341232636</v>
+        <v>0.03065100386362096</v>
       </c>
     </row>
     <row r="141">
@@ -1979,10 +1979,10 @@
         <v>0.162</v>
       </c>
       <c r="B141" t="n">
-        <v>0.001353320945348738</v>
+        <v>0.000870675815320339</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0008980319482070237</v>
+        <v>0.03094259405133777</v>
       </c>
     </row>
     <row r="142">
@@ -1990,10 +1990,10 @@
         <v>0.163</v>
       </c>
       <c r="B142" t="n">
-        <v>0.001327139335954436</v>
+        <v>0.0008522889576950812</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0009049039267572207</v>
+        <v>0.03123580787808694</v>
       </c>
     </row>
     <row r="143">
@@ -2001,10 +2001,10 @@
         <v>0.164</v>
       </c>
       <c r="B143" t="n">
-        <v>0.00130122427414126</v>
+        <v>0.0008341337495996274</v>
       </c>
       <c r="C143" t="n">
-        <v>0.0009117922781929988</v>
+        <v>0.03153065430752454</v>
       </c>
     </row>
     <row r="144">
@@ -2012,10 +2012,10 @@
         <v>0.165</v>
       </c>
       <c r="B144" t="n">
-        <v>0.001276556312456646</v>
+        <v>0.0008168366976340362</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0009186970038242338</v>
+        <v>0.03182714236940935</v>
       </c>
     </row>
     <row r="145">
@@ -2023,10 +2023,10 @@
         <v>0.166</v>
       </c>
       <c r="B145" t="n">
-        <v>0.001252029653104195</v>
+        <v>0.0007996871702514921</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0009256181049608819</v>
+        <v>0.03212528116021343</v>
       </c>
     </row>
     <row r="146">
@@ -2034,10 +2034,10 @@
         <v>0.167</v>
       </c>
       <c r="B146" t="n">
-        <v>0.001227357409530728</v>
+        <v>0.0007825017747249894</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0009325555829130003</v>
+        <v>0.03242507984373929</v>
       </c>
     </row>
     <row r="147">
@@ -2045,10 +2045,10 @@
         <v>0.168</v>
       </c>
       <c r="B147" t="n">
-        <v>0.001203257868591407</v>
+        <v>0.000765738132159926</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0009395094389907366</v>
+        <v>0.03272654765174404</v>
       </c>
     </row>
     <row r="148">
@@ -2056,10 +2056,10 @@
         <v>0.169</v>
       </c>
       <c r="B148" t="n">
-        <v>0.001178826481265944</v>
+        <v>0.0007488196576678484</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0009464796745043352</v>
+        <v>0.03302969388457041</v>
       </c>
     </row>
     <row r="149">
@@ -2067,10 +2067,10 @@
         <v>0.17</v>
       </c>
       <c r="B149" t="n">
-        <v>0.001154954950908069</v>
+        <v>0.0007323129084877653</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0009534662907641359</v>
+        <v>0.03333452791178498</v>
       </c>
     </row>
     <row r="150">
@@ -2078,10 +2078,10 @@
         <v>0.171</v>
       </c>
       <c r="B150" t="n">
-        <v>0.001132541403704786</v>
+        <v>0.0007167843593279221</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0009604692890805645</v>
+        <v>0.03364105917282331</v>
       </c>
     </row>
     <row r="151">
@@ -2089,10 +2089,10 @@
         <v>0.172</v>
       </c>
       <c r="B151" t="n">
-        <v>0.001108848642206541</v>
+        <v>0.0007004997416659875</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0009674886707641486</v>
+        <v>0.03394929717764251</v>
       </c>
     </row>
     <row r="152">
@@ -2100,10 +2100,10 @@
         <v>0.173</v>
       </c>
       <c r="B152" t="n">
-        <v>0.0010856450865098</v>
+        <v>0.0006845786410263917</v>
       </c>
       <c r="C152" t="n">
-        <v>0.0009745244371255049</v>
+        <v>0.03425925150738097</v>
       </c>
     </row>
     <row r="153">
@@ -2111,10 +2111,10 @@
         <v>0.174</v>
       </c>
       <c r="B153" t="n">
-        <v>0.001063192252976287</v>
+        <v>0.0006691839560197954</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0009815765894753458</v>
+        <v>0.03457093181502569</v>
       </c>
     </row>
     <row r="154">
@@ -2122,10 +2122,10 @@
         <v>0.175</v>
       </c>
       <c r="B154" t="n">
-        <v>0.001040730962712288</v>
+        <v>0.0006538361196487876</v>
       </c>
       <c r="C154" t="n">
-        <v>0.0009886451291244772</v>
+        <v>0.03488434782608696</v>
       </c>
     </row>
     <row r="155">
@@ -2133,10 +2133,10 @@
         <v>0.176</v>
       </c>
       <c r="B155" t="n">
-        <v>0.001018723873808417</v>
+        <v>0.0006388252910677384</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0009957300573837982</v>
+        <v>0.03519950933928074</v>
       </c>
     </row>
     <row r="156">
@@ -2144,10 +2144,10 @@
         <v>0.177</v>
       </c>
       <c r="B156" t="n">
-        <v>0.0009969865439023121</v>
+        <v>0.0006240344432117927</v>
       </c>
       <c r="C156" t="n">
-        <v>0.001002831375564303</v>
+        <v>0.03551642622721878</v>
       </c>
     </row>
     <row r="157">
@@ -2155,10 +2155,10 @@
         <v>0.178</v>
       </c>
       <c r="B157" t="n">
-        <v>0.000974881185649255</v>
+        <v>0.0006090641764778019</v>
       </c>
       <c r="C157" t="n">
-        <v>0.001009949084977076</v>
+        <v>0.03583510843710647</v>
       </c>
     </row>
     <row r="158">
@@ -2166,10 +2166,10 @@
         <v>0.179</v>
       </c>
       <c r="B158" t="n">
-        <v>0.0009533136326361887</v>
+        <v>0.0005944806517771254</v>
       </c>
       <c r="C158" t="n">
-        <v>0.001017083186933303</v>
+        <v>0.03615556599144881</v>
       </c>
     </row>
     <row r="159">
@@ -2177,10 +2177,10 @@
         <v>0.18</v>
       </c>
       <c r="B159" t="n">
-        <v>0.0009319841526433732</v>
+        <v>0.0005800954337051771</v>
       </c>
       <c r="C159" t="n">
-        <v>0.001024233682744256</v>
+        <v>0.03647780898876404</v>
       </c>
     </row>
     <row r="160">
@@ -2188,10 +2188,10 @@
         <v>0.181</v>
       </c>
       <c r="B160" t="n">
-        <v>0.0009113886954472569</v>
+        <v>0.0005662158126268119</v>
       </c>
       <c r="C160" t="n">
-        <v>0.001031400573721301</v>
+        <v>0.03680184760430591</v>
       </c>
     </row>
     <row r="161">
@@ -2199,10 +2199,10 @@
         <v>0.182</v>
       </c>
       <c r="B161" t="n">
-        <v>0.0008901959147560873</v>
+        <v>0.000552013657789283</v>
       </c>
       <c r="C161" t="n">
-        <v>0.001038583861175904</v>
+        <v>0.03712769209079374</v>
       </c>
     </row>
     <row r="162">
@@ -2210,10 +2210,10 @@
         <v>0.183</v>
       </c>
       <c r="B162" t="n">
-        <v>0.0008693196726984073</v>
+        <v>0.0005380566840011514</v>
       </c>
       <c r="C162" t="n">
-        <v>0.001045783546419622</v>
+        <v>0.03745535277915107</v>
       </c>
     </row>
     <row r="163">
@@ -2221,10 +2221,10 @@
         <v>0.184</v>
       </c>
       <c r="B163" t="n">
-        <v>0.0008492557049562232</v>
+        <v>0.0005246500439736797</v>
       </c>
       <c r="C163" t="n">
-        <v>0.001052999630764101</v>
+        <v>0.03778484007925276</v>
       </c>
     </row>
     <row r="164">
@@ -2232,10 +2232,10 @@
         <v>0.185</v>
       </c>
       <c r="B164" t="n">
-        <v>0.0008288453324057965</v>
+        <v>0.0005110764497310396</v>
       </c>
       <c r="C164" t="n">
-        <v>0.001060232115521087</v>
+        <v>0.03811616448068061</v>
       </c>
     </row>
     <row r="165">
@@ -2243,10 +2243,10 @@
         <v>0.186</v>
       </c>
       <c r="B165" t="n">
-        <v>0.0008085916769874055</v>
+        <v>0.0004976467602641532</v>
       </c>
       <c r="C165" t="n">
-        <v>0.001067481002002417</v>
+        <v>0.03844933655348771</v>
       </c>
     </row>
     <row r="166">
@@ -2254,10 +2254,10 @@
         <v>0.187</v>
       </c>
       <c r="B166" t="n">
-        <v>0.0007883399484189985</v>
+        <v>0.0004842653468942569</v>
       </c>
       <c r="C166" t="n">
-        <v>0.001074746291520022</v>
+        <v>0.0387843669489716</v>
       </c>
     </row>
     <row r="167">
@@ -2265,10 +2265,10 @@
         <v>0.188</v>
       </c>
       <c r="B167" t="n">
-        <v>0.0007688457930359845</v>
+        <v>0.0004713955093538374</v>
       </c>
       <c r="C167" t="n">
-        <v>0.001082027985385933</v>
+        <v>0.03912126640045636</v>
       </c>
     </row>
     <row r="168">
@@ -2276,10 +2276,10 @@
         <v>0.189</v>
       </c>
       <c r="B168" t="n">
-        <v>0.0007492819499118811</v>
+        <v>0.000458528357920871</v>
       </c>
       <c r="C168" t="n">
-        <v>0.001089326084912264</v>
+        <v>0.03946004572408374</v>
       </c>
     </row>
     <row r="169">
@@ -2287,10 +2287,10 @@
         <v>0.19</v>
       </c>
       <c r="B169" t="n">
-        <v>0.0007294215859846776</v>
+        <v>0.0004455255915827414</v>
       </c>
       <c r="C169" t="n">
-        <v>0.001096640591411228</v>
+        <v>0.03980071581961345</v>
       </c>
     </row>
     <row r="170">
@@ -2298,10 +2298,10 @@
         <v>0.191</v>
       </c>
       <c r="B170" t="n">
-        <v>0.0007097244690700113</v>
+        <v>0.0004326685373108223</v>
       </c>
       <c r="C170" t="n">
-        <v>0.001103971506195131</v>
+        <v>0.04014328767123287</v>
       </c>
     </row>
     <row r="171">
@@ -2309,10 +2309,10 @@
         <v>0.192</v>
       </c>
       <c r="B171" t="n">
-        <v>0.0006909973070278682</v>
+        <v>0.0004204474819786104</v>
       </c>
       <c r="C171" t="n">
-        <v>0.001111318830576381</v>
+        <v>0.04048777234837597</v>
       </c>
     </row>
     <row r="172">
@@ -2320,10 +2320,10 @@
         <v>0.193</v>
       </c>
       <c r="B172" t="n">
-        <v>0.0006719587446188595</v>
+        <v>0.0004080808738837499</v>
       </c>
       <c r="C172" t="n">
-        <v>0.001118682565867468</v>
+        <v>0.04083418100655194</v>
       </c>
     </row>
     <row r="173">
@@ -2331,10 +2331,10 @@
         <v>0.194</v>
       </c>
       <c r="B173" t="n">
-        <v>0.0006529103338654877</v>
+        <v>0.0003957525858354074</v>
       </c>
       <c r="C173" t="n">
-        <v>0.001126062713380977</v>
+        <v>0.04118252488818352</v>
       </c>
     </row>
     <row r="174">
@@ -2342,10 +2342,10 @@
         <v>0.195</v>
       </c>
       <c r="B174" t="n">
-        <v>0.0006336506118971992</v>
+        <v>0.0003833407764597876</v>
       </c>
       <c r="C174" t="n">
-        <v>0.001133459274429598</v>
+        <v>0.04153281532345501</v>
       </c>
     </row>
     <row r="175">
@@ -2353,10 +2353,10 @@
         <v>0.196</v>
       </c>
       <c r="B175" t="n">
-        <v>0.0006150151893237409</v>
+        <v>0.0003713507353992179</v>
       </c>
       <c r="C175" t="n">
-        <v>0.001140872250326106</v>
+        <v>0.04188506373117033</v>
       </c>
     </row>
     <row r="176">
@@ -2364,10 +2364,10 @@
         <v>0.197</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0005965844410374766</v>
+        <v>0.00035952740122087</v>
       </c>
       <c r="C176" t="n">
-        <v>0.001148301642383368</v>
+        <v>0.04223928161962122</v>
       </c>
     </row>
     <row r="177">
@@ -2375,10 +2375,10 @@
         <v>0.198</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0005782461815504464</v>
+        <v>0.0003478025852340184</v>
       </c>
       <c r="C177" t="n">
-        <v>0.001155747451914349</v>
+        <v>0.04259548058746547</v>
       </c>
     </row>
     <row r="178">
@@ -2386,10 +2386,10 @@
         <v>0.199</v>
       </c>
       <c r="B178" t="n">
-        <v>0.0005593268697460056</v>
+        <v>0.0003357716317554175</v>
       </c>
       <c r="C178" t="n">
-        <v>0.001163209680232109</v>
+        <v>0.04295367232461571</v>
       </c>
     </row>
     <row r="179">
@@ -2397,10 +2397,10 @@
         <v>0.2</v>
       </c>
       <c r="B179" t="n">
-        <v>0.0005409472900315399</v>
+        <v>0.0003241080914345477</v>
       </c>
       <c r="C179" t="n">
-        <v>0.001170688328649802</v>
+        <v>0.04331386861313868</v>
       </c>
     </row>
     <row r="180">
@@ -2408,10 +2408,10 @@
         <v>0.201</v>
       </c>
       <c r="B180" t="n">
-        <v>0.0005225453374478148</v>
+        <v>0.0003126678140952324</v>
       </c>
       <c r="C180" t="n">
-        <v>0.001177455557163843</v>
+        <v>0.04362203616536078</v>
       </c>
     </row>
     <row r="181">
@@ -2419,10 +2419,10 @@
         <v>0.202</v>
       </c>
       <c r="B181" t="n">
-        <v>0.0005044579966475957</v>
+        <v>0.000301444734584668</v>
       </c>
       <c r="C181" t="n">
-        <v>0.001184231911462269</v>
+        <v>0.04393136307746354</v>
       </c>
     </row>
     <row r="182">
@@ -2430,10 +2430,10 @@
         <v>0.203</v>
       </c>
       <c r="B182" t="n">
-        <v>0.0004863932428110783</v>
+        <v>0.0002902638342879336</v>
       </c>
       <c r="C182" t="n">
-        <v>0.001191017392042012</v>
+        <v>0.04424185403963414</v>
       </c>
     </row>
     <row r="183">
@@ -2441,10 +2441,10 @@
         <v>0.204</v>
       </c>
       <c r="B183" t="n">
-        <v>0.000468033252738117</v>
+        <v>0.0002789356466375439</v>
       </c>
       <c r="C183" t="n">
-        <v>0.001197811999400034</v>
+        <v>0.0445535137673927</v>
       </c>
     </row>
     <row r="184">
@@ -2452,10 +2452,10 @@
         <v>0.205</v>
       </c>
       <c r="B184" t="n">
-        <v>0.0004497576158755682</v>
+        <v>0.0002676868004394502</v>
       </c>
       <c r="C184" t="n">
-        <v>0.001204615734033312</v>
+        <v>0.04486634700176367</v>
       </c>
     </row>
     <row r="185">
@@ -2463,10 +2463,10 @@
         <v>0.206</v>
       </c>
       <c r="B185" t="n">
-        <v>0.0004317604088357138</v>
+        <v>0.0002566324528733862</v>
       </c>
       <c r="C185" t="n">
-        <v>0.001211428596438865</v>
+        <v>0.0451803585094484</v>
       </c>
     </row>
     <row r="186">
@@ -2474,10 +2474,10 @@
         <v>0.207</v>
       </c>
       <c r="B186" t="n">
-        <v>0.0004140693568488796</v>
+        <v>0.0002457883998783251</v>
       </c>
       <c r="C186" t="n">
-        <v>0.001218250587113712</v>
+        <v>0.0454955530829993</v>
       </c>
     </row>
     <row r="187">
@@ -2485,10 +2485,10 @@
         <v>0.208</v>
       </c>
       <c r="B187" t="n">
-        <v>0.0003957106513425742</v>
+        <v>0.0002345766416580712</v>
       </c>
       <c r="C187" t="n">
-        <v>0.001225081706554921</v>
+        <v>0.04581193554099521</v>
       </c>
     </row>
     <row r="188">
@@ -2496,10 +2496,10 @@
         <v>0.209</v>
       </c>
       <c r="B188" t="n">
-        <v>0.0003775054515516644</v>
+        <v>0.0002234848999607208</v>
       </c>
       <c r="C188" t="n">
-        <v>0.001231921955259565</v>
+        <v>0.04612951072821846</v>
       </c>
     </row>
     <row r="189">
@@ -2507,10 +2507,10 @@
         <v>0.21</v>
       </c>
       <c r="B189" t="n">
-        <v>0.0003594420893290244</v>
+        <v>0.0002125059124141054</v>
       </c>
       <c r="C189" t="n">
-        <v>0.001238771333724749</v>
+        <v>0.04644828351583308</v>
       </c>
     </row>
     <row r="190">
@@ -2518,10 +2518,10 @@
         <v>0.211</v>
       </c>
       <c r="B190" t="n">
-        <v>0.0003416855244427328</v>
+        <v>0.0002017367376966844</v>
       </c>
       <c r="C190" t="n">
-        <v>0.001245629842447611</v>
+        <v>0.04676825880156472</v>
       </c>
     </row>
     <row r="191">
@@ -2529,10 +2529,10 @@
         <v>0.212</v>
       </c>
       <c r="B191" t="n">
-        <v>0.0003230017165252306</v>
+        <v>0.0001904490287739075</v>
       </c>
       <c r="C191" t="n">
-        <v>0.001252497481925289</v>
+        <v>0.04708944150988188</v>
       </c>
     </row>
     <row r="192">
@@ -2540,10 +2540,10 @@
         <v>0.213</v>
       </c>
       <c r="B192" t="n">
-        <v>0.000303378141051622</v>
+        <v>0.0001786376213450908</v>
       </c>
       <c r="C192" t="n">
-        <v>0.001259374252654977</v>
+        <v>0.04741183659217876</v>
       </c>
     </row>
     <row r="193">
@@ -2551,10 +2551,10 @@
         <v>0.214</v>
       </c>
       <c r="B193" t="n">
-        <v>0.0002839162068822302</v>
+        <v>0.0001669524219136723</v>
       </c>
       <c r="C193" t="n">
-        <v>0.001266260155133863</v>
+        <v>0.04773544902695946</v>
       </c>
     </row>
     <row r="194">
@@ -2562,10 +2562,10 @@
         <v>0.215</v>
       </c>
       <c r="B194" t="n">
-        <v>0.0002649006596258086</v>
+        <v>0.0001555602611080955</v>
       </c>
       <c r="C194" t="n">
-        <v>0.00127315518985918</v>
+        <v>0.04806028382002384</v>
       </c>
     </row>
     <row r="195">
@@ -2573,10 +2573,10 @@
         <v>0.216</v>
       </c>
       <c r="B195" t="n">
-        <v>0.0002460875386649329</v>
+        <v>0.0001443170074223657</v>
       </c>
       <c r="C195" t="n">
-        <v>0.001280059357328178</v>
+        <v>0.04838634600465476</v>
       </c>
     </row>
     <row r="196">
@@ -2584,10 +2584,10 @@
         <v>0.217</v>
       </c>
       <c r="B196" t="n">
-        <v>0.000227237058223811</v>
+        <v>0.0001330817492937183</v>
       </c>
       <c r="C196" t="n">
-        <v>0.001286972658038131</v>
+        <v>0.0487136406418071</v>
       </c>
     </row>
     <row r="197">
@@ -2595,10 +2595,10 @@
         <v>0.218</v>
       </c>
       <c r="B197" t="n">
-        <v>0.0002084855964624248</v>
+        <v>0.0001219343391609128</v>
       </c>
       <c r="C197" t="n">
-        <v>0.001293895092486332</v>
+        <v>0.04904217282029801</v>
       </c>
     </row>
     <row r="198">
@@ -2606,10 +2606,10 @@
         <v>0.219</v>
       </c>
       <c r="B198" t="n">
-        <v>0.0001900528142789551</v>
+        <v>0.0001110028385641698</v>
       </c>
       <c r="C198" t="n">
-        <v>0.00130082666117011</v>
+        <v>0.04937194765699904</v>
       </c>
     </row>
     <row r="199">
@@ -2617,10 +2617,10 @@
         <v>0.22</v>
       </c>
       <c r="B199" t="n">
-        <v>0.0001719424583261487</v>
+        <v>0.0001002886750789563</v>
       </c>
       <c r="C199" t="n">
-        <v>0.001307767364586812</v>
+        <v>0.0497029702970297</v>
       </c>
     </row>
     <row r="200">
@@ -2628,10 +2628,10 @@
         <v>0.221</v>
       </c>
       <c r="B200" t="n">
-        <v>0.0001444550869259932</v>
+        <v>8.414140454813476e-05</v>
       </c>
       <c r="C200" t="n">
-        <v>0.00131471720323381</v>
+        <v>0.05003524591395264</v>
       </c>
     </row>
     <row r="201">
@@ -2639,10 +2639,10 @@
         <v>0.222</v>
       </c>
       <c r="B201" t="n">
-        <v>0.0001074529303046294</v>
+        <v>6.25032365381111e-05</v>
       </c>
       <c r="C201" t="n">
-        <v>0.001321676177608493</v>
+        <v>0.0503687797099705</v>
       </c>
     </row>
     <row r="202">
@@ -2650,10 +2650,10 @@
         <v>0.223</v>
       </c>
       <c r="B202" t="n">
-        <v>7.101243974889217e-05</v>
+        <v>4.125011568355088e-05</v>
       </c>
       <c r="C202" t="n">
-        <v>0.00132864428820829</v>
+        <v>0.05070357691612437</v>
       </c>
     </row>
     <row r="203">
@@ -2661,10 +2661,10 @@
         <v>0.224</v>
       </c>
       <c r="B203" t="n">
-        <v>3.519891406379643e-05</v>
+        <v>2.04185859237331e-05</v>
       </c>
       <c r="C203" t="n">
-        <v>0.001335621535530636</v>
+        <v>0.05103964279249381</v>
       </c>
     </row>
     <row r="204">
@@ -2675,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="C204" t="n">
-        <v>0.001342607920073003</v>
+        <v>0.05137698262839878</v>
       </c>
     </row>
   </sheetData>
